--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R18cb06769c254826"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7de902c51438461f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7de902c51438461f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3ccc8fe9d1b94bd9"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3ccc8fe9d1b94bd9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re2b0d35dcd7a443c"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re2b0d35dcd7a443c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9fb0ca170a634d06"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9fb0ca170a634d06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf0a51a820b974db4"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf0a51a820b974db4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6fe602282a954eb1"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6fe602282a954eb1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R276c756b31e54d06"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R276c756b31e54d06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf8738b320e1747b0"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf8738b320e1747b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3a9d41f203104f50"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3a9d41f203104f50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R654ba0f4b2224032"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R654ba0f4b2224032"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbfbc99b91f96484c"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbfbc99b91f96484c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3378257a41434b72"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3378257a41434b72"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc9506545df3b4c28"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc9506545df3b4c28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R53d6def547304c2e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R53d6def547304c2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9486e29edc3f4ccc"/>
   </x:sheets>
 </x:workbook>
 </file>
